--- a/Pagina WEB - Relación de Proveedores e Influencer de la PH.xlsx
+++ b/Pagina WEB - Relación de Proveedores e Influencer de la PH.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10. SIGA PH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DEE7F41-0B0A-40D9-BD37-AA2A5AA7AF07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D7CDEE7-5DED-44DF-B463-F0BCFFD165B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{82BA444D-32AC-4ADB-8060-7C99B47ACAD6}"/>
   </bookViews>
